--- a/sheets/대금율보/검수/이별의 부산정거장.xlsx
+++ b/sheets/대금율보/검수/이별의 부산정거장.xlsx
@@ -6536,7 +6536,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
@@ -6712,7 +6712,7 @@
       <c r="M6" s="24"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="O6" s="24"/>
@@ -6895,7 +6895,7 @@
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
-汏‹</t>
+汏</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汏‹
+          <t xml:space="preserve">汏
 –潢</t>
         </is>
       </c>
@@ -7122,7 +7122,7 @@
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-淋‹</t>
+淋</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -7273,7 +7273,7 @@
       <c r="K16" s="23"/>
       <c r="L16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕‹
+          <t xml:space="preserve">潕
 –湳</t>
         </is>
       </c>
@@ -7305,7 +7305,7 @@
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="G17" s="23"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –汏</t>
         </is>
       </c>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="L20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –㶋</t>
         </is>
       </c>
@@ -7836,7 +7836,7 @@
       <c r="L26" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="M26" s="24"/>

--- a/sheets/대금율보/검수/이별의 부산정거장.xlsx
+++ b/sheets/대금율보/검수/이별의 부산정거장.xlsx
@@ -6433,26 +6433,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="85.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.43" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.43" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.43" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.43" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.43" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.43" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="O8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.43" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="O9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.43" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="O10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.43" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="25" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.43" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="O12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.43" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.43" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
       </c>
       <c r="O14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.43" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.43" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.43" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="O17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.43" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O18" s="24"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.43" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="O19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.43" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="O20" s="23"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.43" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="O21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.43" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="25" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="O22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="63.43" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="63.43" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="O24" s="23"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="63.43" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="23"/>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="O25" s="23"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="63.43" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="24"/>
@@ -7854,6 +7854,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="47"/>
 </worksheet>
 </file>